--- a/data/trans_dic/P3A$otraNOcobra-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraNOcobra-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y no cobra por ello se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y no cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 11,78</t>
+          <t>3,31; 12,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,79</t>
+          <t>3,77; 7,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 9,09</t>
+          <t>4,01; 8,84</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,46</t>
+          <t>1,67; 4,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,8; 8,29</t>
+          <t>5,04; 8,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 6,04</t>
+          <t>3,6; 5,91</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,06</t>
+          <t>2,48; 6,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,46</t>
+          <t>3,2; 6,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,25; 5,73</t>
+          <t>3,21; 5,52</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,75</t>
+          <t>1,59; 5,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,47</t>
+          <t>2,13; 5,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,63</t>
+          <t>2,37; 4,84</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,49</t>
+          <t>2,66; 7,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,45</t>
+          <t>1,44; 4,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,98</t>
+          <t>2,22; 5,03</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,36; 6,66</t>
+          <t>3,52; 6,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,3; 9,53</t>
+          <t>5,16; 9,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,67; 7,36</t>
+          <t>4,65; 7,34</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,45</t>
+          <t>1,84; 4,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,05</t>
+          <t>0,77; 2,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,25</t>
+          <t>1,42; 3,3</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,14</t>
+          <t>0,5; 2,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,85</t>
+          <t>2,02; 3,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,6</t>
+          <t>1,15; 2,59</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,77</t>
+          <t>2,29; 3,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,2; 4,47</t>
+          <t>3,16; 4,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,07; 3,98</t>
+          <t>2,92; 3,95</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y no cobra por ello se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y no cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9893; 36684</t>
+          <t>10307; 39557</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11204; 22555</t>
+          <t>10929; 22020</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23994; 54620</t>
+          <t>24109; 53129</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8269; 23111</t>
+          <t>8671; 23482</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24731; 42681</t>
+          <t>25932; 43208</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37470; 62374</t>
+          <t>37164; 61047</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7534; 19125</t>
+          <t>7820; 18970</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11555; 22476</t>
+          <t>11132; 22593</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21571; 38007</t>
+          <t>21264; 36609</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5012; 14852</t>
+          <t>4983; 15991</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10490; 26042</t>
+          <t>10127; 26203</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18733; 36521</t>
+          <t>18680; 38148</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4771; 13357</t>
+          <t>4747; 13719</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3554; 11510</t>
+          <t>3725; 12007</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9363; 21757</t>
+          <t>9684; 21986</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9051; 17961</t>
+          <t>9496; 18430</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13628; 24500</t>
+          <t>13268; 24259</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24582; 38756</t>
+          <t>24492; 38651</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11498; 27794</t>
+          <t>11479; 27543</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7580; 25892</t>
+          <t>6540; 25258</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21157; 47906</t>
+          <t>20968; 48643</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4659; 19882</t>
+          <t>4605; 20064</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14533; 27600</t>
+          <t>14529; 26909</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>18387; 42821</t>
+          <t>19003; 42583</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>80790; 130554</t>
+          <t>79067; 129235</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>118675; 165885</t>
+          <t>117353; 167125</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>219839; 285265</t>
+          <t>209298; 283026</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$otraNOcobra-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraNOcobra-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 12,7</t>
+          <t>2,94; 8,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 7,6</t>
+          <t>3,6; 7,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 8,84</t>
+          <t>3,79; 6,8</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,53</t>
+          <t>1,58; 4,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,39</t>
+          <t>4,85; 8,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 5,91</t>
+          <t>3,61; 5,98</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 6,01</t>
+          <t>2,32; 5,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,49</t>
+          <t>3,31; 6,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 5,52</t>
+          <t>3,2; 5,64</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,12</t>
+          <t>1,32; 4,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,51</t>
+          <t>3,31; 6,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,84</t>
+          <t>2,71; 4,85</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,7</t>
+          <t>2,33; 6,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,64</t>
+          <t>2,22; 5,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 5,03</t>
+          <t>2,71; 5,32</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,52; 6,83</t>
+          <t>3,25; 6,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,16; 9,44</t>
+          <t>5,24; 9,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,34</t>
+          <t>4,7; 7,36</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,41</t>
+          <t>1,76; 4,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,97</t>
+          <t>1,94; 3,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,3</t>
+          <t>2,13; 3,63</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,16</t>
+          <t>1,03; 2,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,75</t>
+          <t>1,95; 3,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,59</t>
+          <t>1,67; 2,91</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,74</t>
+          <t>2,52; 3,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,16; 4,5</t>
+          <t>3,75; 4,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,92; 3,95</t>
+          <t>3,33; 4,03</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18070</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15998</t>
+          <t>16932</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34068</t>
+          <t>31790</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10307; 39557</t>
+          <t>9359; 26867</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10929; 22020</t>
+          <t>11380; 23158</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24109; 53129</t>
+          <t>24091; 43178</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14430</t>
+          <t>14919</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>33801</t>
+          <t>35224</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48231</t>
+          <t>50143</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8671; 23482</t>
+          <t>8401; 24357</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25932; 43208</t>
+          <t>26482; 46026</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37164; 61047</t>
+          <t>38902; 64433</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12337</t>
+          <t>11907</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28625</t>
+          <t>28401</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7820; 18970</t>
+          <t>7302; 18440</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11132; 22593</t>
+          <t>11739; 22880</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21264; 36609</t>
+          <t>21457; 37827</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9049</t>
+          <t>9544</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>19372</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>27207</t>
+          <t>28917</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4983; 15991</t>
+          <t>4944; 15873</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10127; 26203</t>
+          <t>13967; 25974</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18680; 38148</t>
+          <t>21553; 38547</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>16154</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4747; 13719</t>
+          <t>4782; 14073</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3725; 12007</t>
+          <t>5079; 11745</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9684; 21986</t>
+          <t>11745; 23086</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>13095</t>
+          <t>13163</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>18019</t>
+          <t>18283</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31114</t>
+          <t>31446</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9496; 18430</t>
+          <t>8788; 18052</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13268; 24259</t>
+          <t>13817; 24808</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24492; 38651</t>
+          <t>25098; 39328</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>18330</t>
+          <t>20618</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>21396</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35349</t>
+          <t>42014</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11479; 27543</t>
+          <t>12662; 31366</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6540; 25258</t>
+          <t>14982; 29577</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20968; 48643</t>
+          <t>31803; 54182</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>11661</t>
+          <t>13267</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>23256</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31886</t>
+          <t>36523</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4605; 20064</t>
+          <t>8189; 21267</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>14529; 26909</t>
+          <t>16202; 31533</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>19003; 42583</t>
+          <t>27173; 47412</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>105125</t>
+          <t>106749</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>146841</t>
+          <t>158638</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>251965</t>
+          <t>265387</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>79067; 129235</t>
+          <t>88936; 127027</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>117353; 167125</t>
+          <t>140113; 177963</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>209298; 283026</t>
+          <t>241658; 293041</t>
         </is>
       </c>
     </row>
